--- a/source/excel/Excels/constant.xlsx
+++ b/source/excel/Excels/constant.xlsx
@@ -1,25 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\RealServer\source\excel\Excels\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="4245" yWindow="645" windowWidth="28035" windowHeight="15795"/>
+    <workbookView windowWidth="17617" windowHeight="8700"/>
   </bookViews>
   <sheets>
     <sheet name="constant" sheetId="2" r:id="rId1"/>
     <sheet name="字段注释" sheetId="3" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519"/>
-  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
+  <calcPr calcId="191029"/>
+  <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -27,9 +34,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
-  <si>
-    <t>常数名</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+  <si>
+    <t>唯一ID</t>
+  </si>
+  <si>
+    <t>服务器客户端导出标记</t>
   </si>
   <si>
     <t>数值</t>
@@ -71,7 +81,10 @@
     <t>unknown</t>
   </si>
   <si>
-    <t>key:string</t>
+    <t>key:int</t>
+  </si>
+  <si>
+    <t>string</t>
   </si>
   <si>
     <t>int32</t>
@@ -89,15 +102,27 @@
     <t>kvint32[]</t>
   </si>
   <si>
+    <t>client</t>
+  </si>
+  <si>
     <t>(1, 500, 1500)(2, 500, 1500)(3, 500, 1000)(4, 100, 500)</t>
   </si>
   <si>
+    <t>server</t>
+  </si>
+  <si>
     <t>1, 2, 3, 5, 10</t>
   </si>
   <si>
+    <t>all</t>
+  </si>
+  <si>
     <t>(1, 9501, 1)</t>
   </si>
   <si>
+    <t>(4:74011,74391,74031,74321,74351,74191)</t>
+  </si>
+  <si>
     <t>功能名称</t>
   </si>
   <si>
@@ -108,71 +133,39 @@
   </si>
   <si>
     <t>备注</t>
-  </si>
-  <si>
-    <t>(4:74011,74391,74031,74321,74351,74191)</t>
-  </si>
-  <si>
-    <t>aaa</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>a</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.75"/>
-        <color rgb="FF000000"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>aa</t>
-    </r>
-    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9.75"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <strike/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9.75"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <strike/>
-      <sz val="9.75"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9.75"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -180,34 +173,162 @@
       <sz val="10.5"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="10.5"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="2"/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="9.75"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -217,43 +338,197 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCCFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -290,56 +565,329 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -421,23 +969,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -473,23 +1004,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -631,34 +1145,28 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75"/>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="33" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="19" customWidth="1"/>
-    <col min="4" max="4" width="46.140625" customWidth="1"/>
-    <col min="5" max="5" width="35" customWidth="1"/>
-    <col min="6" max="6" width="78" customWidth="1"/>
-    <col min="7" max="7" width="55" customWidth="1"/>
-    <col min="8" max="8" width="35" customWidth="1"/>
+    <col min="1" max="2" width="33" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="5" max="5" width="46.1428571428571" customWidth="1"/>
+    <col min="6" max="6" width="35" customWidth="1"/>
+    <col min="7" max="7" width="78" customWidth="1"/>
+    <col min="8" max="8" width="55" customWidth="1"/>
+    <col min="9" max="9" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -680,13 +1188,16 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>9</v>
@@ -703,115 +1214,130 @@
       <c r="G2" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="H2" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="18.95" customHeight="1">
-      <c r="A4" s="8" t="s">
+    </row>
+    <row r="4" ht="18.95" customHeight="1" spans="1:9">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" ht="18.95" customHeight="1" spans="1:9">
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" s="5" customFormat="1" ht="18.95" customHeight="1" spans="1:9">
+      <c r="A6" s="1">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="G7" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-    </row>
-    <row r="5" spans="1:8" ht="18.95" customHeight="1">
-      <c r="A5" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-    </row>
-    <row r="6" spans="1:8" ht="18.95" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="4"/>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="F7" t="s">
-        <v>27</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75" outlineLevelCol="4"/>
   <cols>
     <col min="4" max="4" width="51" customWidth="1"/>
     <col min="5" max="5" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="13.5">
-      <c r="A1" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>26</v>
+    <row r="1" ht="13.15" spans="1:5">
+      <c r="A1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -821,19 +1347,19 @@
     <col min="1" max="1" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="18.95" customHeight="1">
+    <row r="1" ht="18.95" customHeight="1" spans="1:1">
       <c r="A1" s="1"/>
     </row>
-    <row r="2" spans="1:1" ht="18.95" customHeight="1">
+    <row r="2" ht="18.95" customHeight="1" spans="1:1">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:1" ht="18.95" customHeight="1">
+    <row r="3" ht="18.95" customHeight="1" spans="1:1">
       <c r="A3" s="1"/>
     </row>
-    <row r="4" spans="1:1" ht="18.95" customHeight="1">
+    <row r="4" ht="18.95" customHeight="1" spans="1:1">
       <c r="A4" s="1"/>
     </row>
-    <row r="5" spans="1:1" ht="18.95" customHeight="1">
+    <row r="5" ht="18.95" customHeight="1" spans="1:1">
       <c r="A5" s="1"/>
     </row>
     <row r="6" spans="1:1">
@@ -849,733 +1375,733 @@
       <c r="A9" s="1"/>
     </row>
     <row r="30" spans="2:9">
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="H30" s="4"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="H30" s="1"/>
       <c r="I30" s="1"/>
     </row>
     <row r="31" spans="2:9">
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="H31" s="4"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="H31" s="1"/>
       <c r="I31" s="1"/>
     </row>
     <row r="32" spans="2:9">
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="H32" s="4"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="H32" s="1"/>
       <c r="I32" s="1"/>
     </row>
     <row r="33" spans="2:9">
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="H33" s="4"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="H33" s="1"/>
       <c r="I33" s="1"/>
     </row>
     <row r="34" spans="2:9">
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="H34" s="4"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="H34" s="1"/>
       <c r="I34" s="1"/>
     </row>
     <row r="35" spans="2:9">
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="7"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="2"/>
     </row>
     <row r="36" spans="2:9">
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="H36" s="4"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="H36" s="1"/>
       <c r="I36" s="1"/>
     </row>
     <row r="37" spans="2:9">
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="H37" s="4"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="H37" s="1"/>
       <c r="I37" s="1"/>
     </row>
     <row r="38" spans="2:9">
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="H38" s="4"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="H38" s="1"/>
       <c r="I38" s="1"/>
     </row>
     <row r="39" spans="2:9">
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="H39" s="4"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="H39" s="1"/>
       <c r="I39" s="1"/>
     </row>
     <row r="40" spans="2:9">
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="H40" s="4"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="H40" s="1"/>
       <c r="I40" s="1"/>
     </row>
     <row r="41" spans="2:9">
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
     </row>
     <row r="42" spans="2:9">
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
     </row>
     <row r="43" spans="2:9">
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
     </row>
     <row r="44" spans="2:9">
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
     </row>
     <row r="45" spans="2:9">
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
     </row>
     <row r="46" spans="2:9">
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
     </row>
     <row r="47" spans="2:9">
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
     </row>
     <row r="48" spans="2:9">
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
     </row>
     <row r="49" spans="2:3">
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
     </row>
     <row r="50" spans="2:3">
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
     </row>
     <row r="51" spans="2:3">
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
     </row>
     <row r="52" spans="2:3">
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
     </row>
     <row r="53" spans="2:3">
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
     </row>
     <row r="54" spans="2:3">
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
     </row>
     <row r="55" spans="2:3">
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
     </row>
     <row r="56" spans="2:3">
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
     </row>
     <row r="57" spans="2:3">
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
     </row>
     <row r="58" spans="2:3">
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
     </row>
     <row r="59" spans="2:3">
-      <c r="B59" s="4"/>
-      <c r="C59" s="4"/>
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
     </row>
     <row r="60" spans="2:3">
-      <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
     </row>
     <row r="61" spans="2:3">
-      <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
     </row>
     <row r="62" spans="2:3">
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
     </row>
     <row r="63" spans="2:3">
-      <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
+      <c r="B63" s="1"/>
+      <c r="C63" s="1"/>
     </row>
     <row r="64" spans="2:3">
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
     </row>
     <row r="65" spans="2:3">
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
     </row>
     <row r="66" spans="2:3">
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
     </row>
     <row r="67" spans="2:3">
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
+      <c r="B67" s="1"/>
+      <c r="C67" s="1"/>
     </row>
     <row r="68" spans="2:3">
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
     </row>
     <row r="69" spans="2:3">
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
+      <c r="B69" s="1"/>
+      <c r="C69" s="1"/>
     </row>
     <row r="70" spans="2:3">
-      <c r="B70" s="4"/>
-      <c r="C70" s="4"/>
+      <c r="B70" s="1"/>
+      <c r="C70" s="1"/>
     </row>
     <row r="71" spans="2:3">
-      <c r="B71" s="4"/>
-      <c r="C71" s="4"/>
+      <c r="B71" s="1"/>
+      <c r="C71" s="1"/>
     </row>
     <row r="72" spans="2:3">
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
+      <c r="B72" s="1"/>
+      <c r="C72" s="1"/>
     </row>
     <row r="73" spans="2:3">
-      <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
+      <c r="B73" s="1"/>
+      <c r="C73" s="1"/>
     </row>
     <row r="74" spans="2:3">
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
+      <c r="B74" s="1"/>
+      <c r="C74" s="1"/>
     </row>
     <row r="75" spans="2:3">
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
+      <c r="B75" s="1"/>
+      <c r="C75" s="1"/>
     </row>
     <row r="76" spans="2:3">
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
+      <c r="B76" s="1"/>
+      <c r="C76" s="1"/>
     </row>
     <row r="77" spans="2:3">
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
+      <c r="B77" s="1"/>
+      <c r="C77" s="1"/>
     </row>
     <row r="78" spans="2:3">
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
+      <c r="B78" s="1"/>
+      <c r="C78" s="1"/>
     </row>
     <row r="79" spans="2:3">
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
+      <c r="B79" s="1"/>
+      <c r="C79" s="1"/>
     </row>
     <row r="80" spans="2:3">
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
+      <c r="B80" s="1"/>
+      <c r="C80" s="1"/>
     </row>
     <row r="81" spans="2:3">
-      <c r="B81" s="4"/>
-      <c r="C81" s="4"/>
+      <c r="B81" s="1"/>
+      <c r="C81" s="1"/>
     </row>
     <row r="82" spans="2:3">
-      <c r="B82" s="4"/>
-      <c r="C82" s="4"/>
+      <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
     </row>
     <row r="83" spans="2:3">
-      <c r="B83" s="4"/>
-      <c r="C83" s="4"/>
+      <c r="B83" s="1"/>
+      <c r="C83" s="1"/>
     </row>
     <row r="84" spans="2:3">
-      <c r="B84" s="4"/>
-      <c r="C84" s="4"/>
+      <c r="B84" s="1"/>
+      <c r="C84" s="1"/>
     </row>
     <row r="85" spans="2:3">
-      <c r="B85" s="4"/>
-      <c r="C85" s="4"/>
+      <c r="B85" s="1"/>
+      <c r="C85" s="1"/>
     </row>
     <row r="86" spans="2:3">
-      <c r="B86" s="4"/>
-      <c r="C86" s="4"/>
+      <c r="B86" s="1"/>
+      <c r="C86" s="1"/>
     </row>
     <row r="87" spans="2:3">
-      <c r="B87" s="4"/>
-      <c r="C87" s="4"/>
+      <c r="B87" s="1"/>
+      <c r="C87" s="1"/>
     </row>
     <row r="88" spans="2:3">
-      <c r="B88" s="4"/>
-      <c r="C88" s="4"/>
+      <c r="B88" s="1"/>
+      <c r="C88" s="1"/>
     </row>
     <row r="89" spans="2:3">
-      <c r="B89" s="4"/>
-      <c r="C89" s="4"/>
+      <c r="B89" s="1"/>
+      <c r="C89" s="1"/>
     </row>
     <row r="90" spans="2:3">
-      <c r="B90" s="4"/>
-      <c r="C90" s="4"/>
+      <c r="B90" s="1"/>
+      <c r="C90" s="1"/>
     </row>
     <row r="91" spans="2:3">
-      <c r="B91" s="4"/>
-      <c r="C91" s="4"/>
+      <c r="B91" s="1"/>
+      <c r="C91" s="1"/>
     </row>
     <row r="92" spans="2:3">
-      <c r="B92" s="4"/>
-      <c r="C92" s="4"/>
+      <c r="B92" s="1"/>
+      <c r="C92" s="1"/>
     </row>
     <row r="93" spans="2:3">
-      <c r="B93" s="4"/>
-      <c r="C93" s="4"/>
+      <c r="B93" s="1"/>
+      <c r="C93" s="1"/>
     </row>
     <row r="94" spans="2:3">
-      <c r="B94" s="4"/>
-      <c r="C94" s="4"/>
+      <c r="B94" s="1"/>
+      <c r="C94" s="1"/>
     </row>
     <row r="95" spans="2:3">
-      <c r="B95" s="4"/>
-      <c r="C95" s="4"/>
+      <c r="B95" s="1"/>
+      <c r="C95" s="1"/>
     </row>
     <row r="96" spans="2:3">
-      <c r="B96" s="4"/>
-      <c r="C96" s="4"/>
+      <c r="B96" s="1"/>
+      <c r="C96" s="1"/>
     </row>
     <row r="97" spans="2:3">
-      <c r="B97" s="4"/>
-      <c r="C97" s="4"/>
+      <c r="B97" s="1"/>
+      <c r="C97" s="1"/>
     </row>
     <row r="98" spans="2:3">
-      <c r="B98" s="4"/>
-      <c r="C98" s="4"/>
+      <c r="B98" s="1"/>
+      <c r="C98" s="1"/>
     </row>
     <row r="99" spans="2:3">
-      <c r="B99" s="4"/>
-      <c r="C99" s="4"/>
+      <c r="B99" s="1"/>
+      <c r="C99" s="1"/>
     </row>
     <row r="100" spans="2:3">
-      <c r="B100" s="4"/>
-      <c r="C100" s="4"/>
+      <c r="B100" s="1"/>
+      <c r="C100" s="1"/>
     </row>
     <row r="101" spans="2:3">
-      <c r="B101" s="4"/>
-      <c r="C101" s="4"/>
+      <c r="B101" s="1"/>
+      <c r="C101" s="1"/>
     </row>
     <row r="102" spans="2:3">
-      <c r="B102" s="4"/>
-      <c r="C102" s="4"/>
+      <c r="B102" s="1"/>
+      <c r="C102" s="1"/>
     </row>
     <row r="103" spans="2:3">
-      <c r="B103" s="4"/>
-      <c r="C103" s="4"/>
+      <c r="B103" s="1"/>
+      <c r="C103" s="1"/>
     </row>
     <row r="104" spans="2:3">
-      <c r="B104" s="4"/>
-      <c r="C104" s="4"/>
+      <c r="B104" s="1"/>
+      <c r="C104" s="1"/>
     </row>
     <row r="105" spans="2:3">
-      <c r="B105" s="4"/>
-      <c r="C105" s="4"/>
+      <c r="B105" s="1"/>
+      <c r="C105" s="1"/>
     </row>
     <row r="106" spans="2:3">
-      <c r="B106" s="4"/>
-      <c r="C106" s="4"/>
+      <c r="B106" s="1"/>
+      <c r="C106" s="1"/>
     </row>
     <row r="107" spans="2:3">
-      <c r="B107" s="4"/>
-      <c r="C107" s="4"/>
+      <c r="B107" s="1"/>
+      <c r="C107" s="1"/>
     </row>
     <row r="108" spans="2:3">
-      <c r="B108" s="4"/>
-      <c r="C108" s="4"/>
+      <c r="B108" s="1"/>
+      <c r="C108" s="1"/>
     </row>
     <row r="109" spans="2:3">
-      <c r="B109" s="4"/>
-      <c r="C109" s="4"/>
+      <c r="B109" s="1"/>
+      <c r="C109" s="1"/>
     </row>
     <row r="110" spans="2:3">
-      <c r="B110" s="4"/>
-      <c r="C110" s="4"/>
+      <c r="B110" s="1"/>
+      <c r="C110" s="1"/>
     </row>
     <row r="111" spans="2:3">
-      <c r="B111" s="4"/>
-      <c r="C111" s="4"/>
+      <c r="B111" s="1"/>
+      <c r="C111" s="1"/>
     </row>
     <row r="112" spans="2:3">
-      <c r="B112" s="4"/>
-      <c r="C112" s="4"/>
+      <c r="B112" s="1"/>
+      <c r="C112" s="1"/>
     </row>
     <row r="113" spans="2:3">
-      <c r="B113" s="4"/>
-      <c r="C113" s="4"/>
+      <c r="B113" s="1"/>
+      <c r="C113" s="1"/>
     </row>
     <row r="114" spans="2:3">
-      <c r="B114" s="4"/>
-      <c r="C114" s="4"/>
+      <c r="B114" s="1"/>
+      <c r="C114" s="1"/>
     </row>
     <row r="115" spans="2:3">
-      <c r="B115" s="4"/>
-      <c r="C115" s="4"/>
+      <c r="B115" s="1"/>
+      <c r="C115" s="1"/>
     </row>
     <row r="116" spans="2:3">
-      <c r="B116" s="4"/>
-      <c r="C116" s="4"/>
+      <c r="B116" s="1"/>
+      <c r="C116" s="1"/>
     </row>
     <row r="117" spans="2:3">
-      <c r="B117" s="4"/>
-      <c r="C117" s="4"/>
+      <c r="B117" s="1"/>
+      <c r="C117" s="1"/>
     </row>
     <row r="118" spans="2:3">
-      <c r="B118" s="4"/>
-      <c r="C118" s="4"/>
+      <c r="B118" s="1"/>
+      <c r="C118" s="1"/>
     </row>
     <row r="119" spans="2:3">
-      <c r="B119" s="4"/>
-      <c r="C119" s="4"/>
+      <c r="B119" s="1"/>
+      <c r="C119" s="1"/>
     </row>
     <row r="120" spans="2:3">
-      <c r="B120" s="4"/>
-      <c r="C120" s="4"/>
+      <c r="B120" s="1"/>
+      <c r="C120" s="1"/>
     </row>
     <row r="121" spans="2:3">
-      <c r="B121" s="4"/>
-      <c r="C121" s="4"/>
+      <c r="B121" s="1"/>
+      <c r="C121" s="1"/>
     </row>
     <row r="122" spans="2:3">
-      <c r="B122" s="4"/>
-      <c r="C122" s="4"/>
+      <c r="B122" s="1"/>
+      <c r="C122" s="1"/>
     </row>
     <row r="123" spans="2:3">
-      <c r="B123" s="4"/>
-      <c r="C123" s="4"/>
+      <c r="B123" s="1"/>
+      <c r="C123" s="1"/>
     </row>
     <row r="124" spans="2:3">
-      <c r="B124" s="4"/>
-      <c r="C124" s="4"/>
+      <c r="B124" s="1"/>
+      <c r="C124" s="1"/>
     </row>
     <row r="125" spans="2:3">
-      <c r="B125" s="4"/>
-      <c r="C125" s="4"/>
+      <c r="B125" s="1"/>
+      <c r="C125" s="1"/>
     </row>
     <row r="126" spans="2:3">
-      <c r="B126" s="4"/>
-      <c r="C126" s="4"/>
+      <c r="B126" s="1"/>
+      <c r="C126" s="1"/>
     </row>
     <row r="127" spans="2:3">
-      <c r="B127" s="4"/>
-      <c r="C127" s="4"/>
+      <c r="B127" s="1"/>
+      <c r="C127" s="1"/>
     </row>
     <row r="128" spans="2:3">
-      <c r="B128" s="4"/>
-      <c r="C128" s="4"/>
+      <c r="B128" s="1"/>
+      <c r="C128" s="1"/>
     </row>
     <row r="129" spans="2:3">
-      <c r="B129" s="4"/>
-      <c r="C129" s="4"/>
+      <c r="B129" s="1"/>
+      <c r="C129" s="1"/>
     </row>
     <row r="130" spans="2:3">
-      <c r="B130" s="4"/>
-      <c r="C130" s="4"/>
+      <c r="B130" s="1"/>
+      <c r="C130" s="1"/>
     </row>
     <row r="131" spans="2:3">
-      <c r="B131" s="4"/>
-      <c r="C131" s="4"/>
+      <c r="B131" s="1"/>
+      <c r="C131" s="1"/>
     </row>
     <row r="132" spans="2:3">
-      <c r="B132" s="4"/>
-      <c r="C132" s="4"/>
+      <c r="B132" s="1"/>
+      <c r="C132" s="1"/>
     </row>
     <row r="133" spans="2:3">
-      <c r="B133" s="4"/>
-      <c r="C133" s="4"/>
+      <c r="B133" s="1"/>
+      <c r="C133" s="1"/>
     </row>
     <row r="134" spans="2:3">
-      <c r="B134" s="4"/>
-      <c r="C134" s="4"/>
+      <c r="B134" s="1"/>
+      <c r="C134" s="1"/>
     </row>
     <row r="135" spans="2:3">
-      <c r="B135" s="4"/>
-      <c r="C135" s="4"/>
+      <c r="B135" s="1"/>
+      <c r="C135" s="1"/>
     </row>
     <row r="136" spans="2:3">
-      <c r="B136" s="4"/>
-      <c r="C136" s="4"/>
+      <c r="B136" s="1"/>
+      <c r="C136" s="1"/>
     </row>
     <row r="137" spans="2:3">
-      <c r="B137" s="4"/>
-      <c r="C137" s="4"/>
+      <c r="B137" s="1"/>
+      <c r="C137" s="1"/>
     </row>
     <row r="138" spans="2:3">
-      <c r="B138" s="4"/>
-      <c r="C138" s="4"/>
+      <c r="B138" s="1"/>
+      <c r="C138" s="1"/>
     </row>
     <row r="139" spans="2:3">
-      <c r="B139" s="4"/>
-      <c r="C139" s="4"/>
+      <c r="B139" s="1"/>
+      <c r="C139" s="1"/>
     </row>
     <row r="140" spans="2:3">
-      <c r="B140" s="4"/>
-      <c r="C140" s="4"/>
+      <c r="B140" s="1"/>
+      <c r="C140" s="1"/>
     </row>
     <row r="141" spans="2:3">
-      <c r="B141" s="4"/>
-      <c r="C141" s="4"/>
+      <c r="B141" s="1"/>
+      <c r="C141" s="1"/>
     </row>
     <row r="142" spans="2:3">
-      <c r="B142" s="4"/>
-      <c r="C142" s="4"/>
+      <c r="B142" s="1"/>
+      <c r="C142" s="1"/>
     </row>
     <row r="143" spans="2:3">
-      <c r="B143" s="4"/>
-      <c r="C143" s="4"/>
+      <c r="B143" s="1"/>
+      <c r="C143" s="1"/>
     </row>
     <row r="144" spans="2:3">
-      <c r="B144" s="4"/>
-      <c r="C144" s="4"/>
+      <c r="B144" s="1"/>
+      <c r="C144" s="1"/>
     </row>
     <row r="145" spans="2:3">
-      <c r="B145" s="4"/>
-      <c r="C145" s="4"/>
+      <c r="B145" s="1"/>
+      <c r="C145" s="1"/>
     </row>
     <row r="146" spans="2:3">
-      <c r="B146" s="4"/>
-      <c r="C146" s="4"/>
+      <c r="B146" s="1"/>
+      <c r="C146" s="1"/>
     </row>
     <row r="147" spans="2:3">
-      <c r="B147" s="4"/>
-      <c r="C147" s="4"/>
+      <c r="B147" s="1"/>
+      <c r="C147" s="1"/>
     </row>
     <row r="148" spans="2:3">
-      <c r="B148" s="4"/>
-      <c r="C148" s="4"/>
+      <c r="B148" s="1"/>
+      <c r="C148" s="1"/>
     </row>
     <row r="149" spans="2:3">
-      <c r="B149" s="4"/>
-      <c r="C149" s="4"/>
+      <c r="B149" s="1"/>
+      <c r="C149" s="1"/>
     </row>
     <row r="150" spans="2:3">
-      <c r="B150" s="4"/>
-      <c r="C150" s="4"/>
+      <c r="B150" s="1"/>
+      <c r="C150" s="1"/>
     </row>
     <row r="151" spans="2:3">
-      <c r="B151" s="4"/>
-      <c r="C151" s="4"/>
+      <c r="B151" s="1"/>
+      <c r="C151" s="1"/>
     </row>
     <row r="152" spans="2:3">
-      <c r="B152" s="4"/>
-      <c r="C152" s="4"/>
+      <c r="B152" s="1"/>
+      <c r="C152" s="1"/>
     </row>
     <row r="153" spans="2:3">
-      <c r="B153" s="4"/>
-      <c r="C153" s="4"/>
+      <c r="B153" s="1"/>
+      <c r="C153" s="1"/>
     </row>
     <row r="154" spans="2:3">
-      <c r="B154" s="4"/>
-      <c r="C154" s="4"/>
+      <c r="B154" s="1"/>
+      <c r="C154" s="1"/>
     </row>
     <row r="155" spans="2:3">
-      <c r="B155" s="4"/>
-      <c r="C155" s="4"/>
+      <c r="B155" s="1"/>
+      <c r="C155" s="1"/>
     </row>
     <row r="156" spans="2:3">
-      <c r="B156" s="4"/>
-      <c r="C156" s="4"/>
+      <c r="B156" s="1"/>
+      <c r="C156" s="1"/>
     </row>
     <row r="157" spans="2:3">
-      <c r="B157" s="4"/>
-      <c r="C157" s="4"/>
+      <c r="B157" s="1"/>
+      <c r="C157" s="1"/>
     </row>
     <row r="158" spans="2:3">
-      <c r="B158" s="4"/>
-      <c r="C158" s="4"/>
+      <c r="B158" s="1"/>
+      <c r="C158" s="1"/>
     </row>
     <row r="159" spans="2:3">
-      <c r="B159" s="4"/>
-      <c r="C159" s="4"/>
+      <c r="B159" s="1"/>
+      <c r="C159" s="1"/>
     </row>
     <row r="160" spans="2:3">
-      <c r="B160" s="4"/>
-      <c r="C160" s="4"/>
+      <c r="B160" s="1"/>
+      <c r="C160" s="1"/>
     </row>
     <row r="161" spans="2:3">
-      <c r="B161" s="4"/>
-      <c r="C161" s="4"/>
+      <c r="B161" s="1"/>
+      <c r="C161" s="1"/>
     </row>
     <row r="162" spans="2:3">
-      <c r="B162" s="4"/>
-      <c r="C162" s="4"/>
+      <c r="B162" s="1"/>
+      <c r="C162" s="1"/>
     </row>
     <row r="163" spans="2:3">
-      <c r="B163" s="4"/>
-      <c r="C163" s="4"/>
+      <c r="B163" s="1"/>
+      <c r="C163" s="1"/>
     </row>
     <row r="164" spans="2:3">
-      <c r="B164" s="4"/>
-      <c r="C164" s="4"/>
+      <c r="B164" s="1"/>
+      <c r="C164" s="1"/>
     </row>
     <row r="165" spans="2:3">
-      <c r="B165" s="4"/>
-      <c r="C165" s="4"/>
+      <c r="B165" s="1"/>
+      <c r="C165" s="1"/>
     </row>
     <row r="166" spans="2:3">
-      <c r="B166" s="4"/>
-      <c r="C166" s="4"/>
+      <c r="B166" s="1"/>
+      <c r="C166" s="1"/>
     </row>
     <row r="167" spans="2:3">
-      <c r="B167" s="4"/>
-      <c r="C167" s="4"/>
+      <c r="B167" s="1"/>
+      <c r="C167" s="1"/>
     </row>
     <row r="168" spans="2:3">
-      <c r="B168" s="4"/>
-      <c r="C168" s="4"/>
+      <c r="B168" s="1"/>
+      <c r="C168" s="1"/>
     </row>
     <row r="169" spans="2:3">
-      <c r="B169" s="4"/>
-      <c r="C169" s="4"/>
+      <c r="B169" s="1"/>
+      <c r="C169" s="1"/>
     </row>
     <row r="170" spans="2:3">
-      <c r="B170" s="4"/>
-      <c r="C170" s="4"/>
+      <c r="B170" s="1"/>
+      <c r="C170" s="1"/>
     </row>
     <row r="171" spans="2:3">
-      <c r="B171" s="4"/>
-      <c r="C171" s="4"/>
+      <c r="B171" s="1"/>
+      <c r="C171" s="1"/>
     </row>
     <row r="172" spans="2:3">
-      <c r="B172" s="4"/>
-      <c r="C172" s="4"/>
+      <c r="B172" s="1"/>
+      <c r="C172" s="1"/>
     </row>
     <row r="173" spans="2:3">
-      <c r="B173" s="4"/>
-      <c r="C173" s="4"/>
+      <c r="B173" s="1"/>
+      <c r="C173" s="1"/>
     </row>
     <row r="174" spans="2:3">
-      <c r="B174" s="4"/>
-      <c r="C174" s="4"/>
+      <c r="B174" s="1"/>
+      <c r="C174" s="1"/>
     </row>
     <row r="175" spans="2:3">
-      <c r="B175" s="4"/>
-      <c r="C175" s="4"/>
+      <c r="B175" s="1"/>
+      <c r="C175" s="1"/>
     </row>
     <row r="176" spans="2:3">
-      <c r="B176" s="4"/>
-      <c r="C176" s="4"/>
+      <c r="B176" s="1"/>
+      <c r="C176" s="1"/>
     </row>
     <row r="177" spans="2:3">
-      <c r="B177" s="4"/>
-      <c r="C177" s="4"/>
+      <c r="B177" s="1"/>
+      <c r="C177" s="1"/>
     </row>
     <row r="178" spans="2:3">
-      <c r="B178" s="4"/>
-      <c r="C178" s="4"/>
+      <c r="B178" s="1"/>
+      <c r="C178" s="1"/>
     </row>
     <row r="179" spans="2:3">
-      <c r="B179" s="4"/>
-      <c r="C179" s="4"/>
+      <c r="B179" s="1"/>
+      <c r="C179" s="1"/>
     </row>
     <row r="180" spans="2:3">
-      <c r="B180" s="4"/>
-      <c r="C180" s="4"/>
+      <c r="B180" s="1"/>
+      <c r="C180" s="1"/>
     </row>
     <row r="181" spans="2:3">
-      <c r="B181" s="4"/>
-      <c r="C181" s="4"/>
+      <c r="B181" s="1"/>
+      <c r="C181" s="1"/>
     </row>
     <row r="182" spans="2:3">
-      <c r="B182" s="4"/>
-      <c r="C182" s="4"/>
+      <c r="B182" s="1"/>
+      <c r="C182" s="1"/>
     </row>
     <row r="183" spans="2:3">
-      <c r="B183" s="4"/>
-      <c r="C183" s="4"/>
+      <c r="B183" s="1"/>
+      <c r="C183" s="1"/>
     </row>
     <row r="184" spans="2:3">
-      <c r="B184" s="4"/>
-      <c r="C184" s="4"/>
+      <c r="B184" s="1"/>
+      <c r="C184" s="1"/>
     </row>
     <row r="185" spans="2:3">
-      <c r="B185" s="4"/>
-      <c r="C185" s="4"/>
+      <c r="B185" s="1"/>
+      <c r="C185" s="1"/>
     </row>
     <row r="186" spans="2:3">
-      <c r="B186" s="4"/>
-      <c r="C186" s="4"/>
+      <c r="B186" s="1"/>
+      <c r="C186" s="1"/>
     </row>
     <row r="187" spans="2:3">
-      <c r="B187" s="4"/>
-      <c r="C187" s="4"/>
+      <c r="B187" s="1"/>
+      <c r="C187" s="1"/>
     </row>
     <row r="188" spans="2:3">
-      <c r="B188" s="4"/>
-      <c r="C188" s="4"/>
+      <c r="B188" s="1"/>
+      <c r="C188" s="1"/>
     </row>
     <row r="189" spans="2:3">
-      <c r="B189" s="4"/>
-      <c r="C189" s="4"/>
+      <c r="B189" s="1"/>
+      <c r="C189" s="1"/>
     </row>
     <row r="190" spans="2:3">
-      <c r="B190" s="4"/>
-      <c r="C190" s="4"/>
+      <c r="B190" s="1"/>
+      <c r="C190" s="1"/>
     </row>
     <row r="191" spans="2:3">
-      <c r="B191" s="4"/>
-      <c r="C191" s="4"/>
+      <c r="B191" s="1"/>
+      <c r="C191" s="1"/>
     </row>
     <row r="192" spans="2:3">
-      <c r="B192" s="4"/>
-      <c r="C192" s="4"/>
+      <c r="B192" s="1"/>
+      <c r="C192" s="1"/>
     </row>
     <row r="193" spans="2:3">
-      <c r="B193" s="4"/>
-      <c r="C193" s="4"/>
+      <c r="B193" s="1"/>
+      <c r="C193" s="1"/>
     </row>
     <row r="194" spans="2:3">
-      <c r="B194" s="4"/>
-      <c r="C194" s="4"/>
+      <c r="B194" s="1"/>
+      <c r="C194" s="1"/>
     </row>
     <row r="195" spans="2:3">
-      <c r="B195" s="4"/>
-      <c r="C195" s="4"/>
+      <c r="B195" s="1"/>
+      <c r="C195" s="1"/>
     </row>
     <row r="196" spans="2:3">
-      <c r="B196" s="4"/>
-      <c r="C196" s="4"/>
+      <c r="B196" s="1"/>
+      <c r="C196" s="1"/>
     </row>
     <row r="197" spans="2:3">
-      <c r="B197" s="4"/>
-      <c r="C197" s="4"/>
+      <c r="B197" s="1"/>
+      <c r="C197" s="1"/>
     </row>
     <row r="198" spans="2:3">
-      <c r="B198" s="4"/>
-      <c r="C198" s="4"/>
+      <c r="B198" s="1"/>
+      <c r="C198" s="1"/>
     </row>
     <row r="199" spans="2:3">
-      <c r="B199" s="4"/>
-      <c r="C199" s="4"/>
+      <c r="B199" s="1"/>
+      <c r="C199" s="1"/>
     </row>
     <row r="200" spans="2:3">
-      <c r="B200" s="4"/>
-      <c r="C200" s="4"/>
+      <c r="B200" s="1"/>
+      <c r="C200" s="1"/>
     </row>
     <row r="201" spans="2:3">
-      <c r="B201" s="4"/>
-      <c r="C201" s="4"/>
+      <c r="B201" s="1"/>
+      <c r="C201" s="1"/>
     </row>
     <row r="202" spans="2:3">
-      <c r="B202" s="4"/>
-      <c r="C202" s="4"/>
+      <c r="B202" s="1"/>
+      <c r="C202" s="1"/>
     </row>
     <row r="203" spans="2:3">
-      <c r="B203" s="4"/>
-      <c r="C203" s="4"/>
+      <c r="B203" s="1"/>
+      <c r="C203" s="1"/>
     </row>
     <row r="204" spans="2:3">
-      <c r="B204" s="4"/>
-      <c r="C204" s="4"/>
+      <c r="B204" s="1"/>
+      <c r="C204" s="1"/>
     </row>
     <row r="205" spans="2:3">
-      <c r="B205" s="4"/>
-      <c r="C205" s="4"/>
+      <c r="B205" s="1"/>
+      <c r="C205" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>